--- a/diseases/d159/2026-2029.xlsx
+++ b/diseases/d159/2026-2029.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
@@ -793,12 +788,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -809,11 +799,6 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>phf_monthly</t>
@@ -878,7 +863,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -913,113 +898,36 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.01891260466471829</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly source-defined rickettsial disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN3" t="b">
-        <v>1</v>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1027,12 +935,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1043,11 +946,6 @@
       <c r="AT3" t="n">
         <v>1</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>phf_monthly</t>
@@ -1147,30 +1045,25 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01891260466471829</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1189,12 +1082,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1205,11 +1093,6 @@
       <c r="AT4" t="n">
         <v>1</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>phf_monthly</t>
@@ -1274,7 +1157,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1309,113 +1192,33 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly source-defined rickettsial disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN5" t="b">
-        <v>1</v>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1423,12 +1226,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1439,11 +1237,6 @@
       <c r="AT5" t="n">
         <v>1</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>phf_monthly</t>
@@ -1543,12 +1336,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1557,17 +1350,9 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
@@ -1585,12 +1370,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1601,11 +1381,6 @@
       <c r="AT6" t="n">
         <v>1</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>phf_monthly</t>
@@ -1670,7 +1445,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1705,12 +1480,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1719,99 +1494,19 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly source-defined rickettsial disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN7" t="b">
-        <v>1</v>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1819,12 +1514,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1835,11 +1525,6 @@
       <c r="AT7" t="n">
         <v>1</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>phf_monthly</t>
@@ -1876,1185 +1561,6 @@
         </is>
       </c>
       <c r="BC7" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>D159</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>rickettsial-disease</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>NZ</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>D159</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>立克次体病</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>D159</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>rickettsial-disease</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NZ</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>D159</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>立克次体病</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly source-defined rickettsial disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>D159</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>rickettsial-disease</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>NZ</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>D159</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>立克次体病</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D159</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>rickettsial-disease</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>NZ</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>D159</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>立克次体病</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly source-defined rickettsial disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>D159</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>rickettsial-disease</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>NZ</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>D159</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>立克次体病</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D159</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>rickettsial-disease</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>NZ</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>D159</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>立克次体病</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Rickettsial disease</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly source-defined rickettsial disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -3186,7 +1692,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -3206,7 +1712,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3216,7 +1722,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d159/2026-2029.xlsx
+++ b/diseases/d159/2026-2029.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
@@ -788,7 +793,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -798,6 +808,11 @@
       </c>
       <c r="AT2" t="n">
         <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -863,7 +878,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -898,36 +913,113 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly source-defined rickettsial disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.01891260466471829</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -935,7 +1027,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -945,6 +1042,11 @@
       </c>
       <c r="AT3" t="n">
         <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1045,25 +1147,30 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.01891260466471829</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1082,7 +1189,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1092,6 +1204,11 @@
       </c>
       <c r="AT4" t="n">
         <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1157,7 +1274,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1192,33 +1309,113 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly source-defined rickettsial disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1226,7 +1423,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1236,6 +1438,11 @@
       </c>
       <c r="AT5" t="n">
         <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1336,12 +1543,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1350,9 +1557,17 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
@@ -1370,7 +1585,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1380,6 +1600,11 @@
       </c>
       <c r="AT6" t="n">
         <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1445,7 +1670,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1480,12 +1705,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1494,19 +1719,99 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
         </is>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly source-defined rickettsial disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1514,7 +1819,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1525,6 +1835,11 @@
       <c r="AT7" t="n">
         <v>1</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>phf_monthly</t>
@@ -1561,6 +1876,1185 @@
         </is>
       </c>
       <c r="BC7" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D159</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>rickettsial-disease</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>D159</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>立克次体病</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D159</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>rickettsial-disease</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D159</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>立克次体病</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly source-defined rickettsial disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D159</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>rickettsial-disease</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D159</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>立克次体病</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D159</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>rickettsial-disease</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D159</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>立克次体病</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly source-defined rickettsial disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D159</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>rickettsial-disease</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D159</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>立克次体病</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D159</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rickettsial-disease</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D159</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>立克次体病</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Rickettsial disease</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly source-defined rickettsial disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_NZ_RICKETTSIAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1692,7 +3186,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -1712,7 +3206,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1722,7 +3216,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
